--- a/data/raw/sales/Week 30/Audio_Array/other_channels.xlsx
+++ b/data/raw/sales/Week 30/Audio_Array/other_channels.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\Nitesh Gdrive\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\sales\Week 30\Audio_Array\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82C28D28-8C92-45FC-8E75-9562635393E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91B5C55A-3900-45DA-B715-AC362F422BFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="164">
   <si>
     <t>SKU</t>
   </si>
@@ -257,13 +257,289 @@
   </si>
   <si>
     <t>PB-12 (AM-C11+AA-05+AI-04+AH-60-RD)</t>
+  </si>
+  <si>
+    <t>FBA76863</t>
+  </si>
+  <si>
+    <t>AI-03</t>
+  </si>
+  <si>
+    <t>FBA78925</t>
+  </si>
+  <si>
+    <t>AM-C11X</t>
+  </si>
+  <si>
+    <t>AI-04 Red</t>
+  </si>
+  <si>
+    <t>FBA79011</t>
+  </si>
+  <si>
+    <t>AM-C43</t>
+  </si>
+  <si>
+    <t>FBA79009</t>
+  </si>
+  <si>
+    <t>AM-C41</t>
+  </si>
+  <si>
+    <t>FBA79010</t>
+  </si>
+  <si>
+    <t>AM-C42</t>
+  </si>
+  <si>
+    <t>FBA79444</t>
+  </si>
+  <si>
+    <t>AM-W20</t>
+  </si>
+  <si>
+    <t>FBA79064</t>
+  </si>
+  <si>
+    <t>AA-25</t>
+  </si>
+  <si>
+    <t>FBA77171</t>
+  </si>
+  <si>
+    <t>AC-6XL</t>
+  </si>
+  <si>
+    <t>FBA79356</t>
+  </si>
+  <si>
+    <t>AA-19WL</t>
+  </si>
+  <si>
+    <t>FBA79445</t>
+  </si>
+  <si>
+    <t>AM-W32</t>
+  </si>
+  <si>
+    <t>FBA78960</t>
+  </si>
+  <si>
+    <t>AM-C39</t>
+  </si>
+  <si>
+    <t>FBA79104</t>
+  </si>
+  <si>
+    <t>AI-11</t>
+  </si>
+  <si>
+    <t>FBA79106</t>
+  </si>
+  <si>
+    <t>AM-C44</t>
+  </si>
+  <si>
+    <t>FBA79008</t>
+  </si>
+  <si>
+    <t>AI-06</t>
+  </si>
+  <si>
+    <t>FBA75691</t>
+  </si>
+  <si>
+    <t>AM-W14</t>
+  </si>
+  <si>
+    <t>FBA79449</t>
+  </si>
+  <si>
+    <t>AM-W36</t>
+  </si>
+  <si>
+    <t>FBA75679</t>
+  </si>
+  <si>
+    <t>AA-02</t>
+  </si>
+  <si>
+    <t>FBA75680</t>
+  </si>
+  <si>
+    <t>AM-C6</t>
+  </si>
+  <si>
+    <t>FBA78973</t>
+  </si>
+  <si>
+    <t>AA-19</t>
+  </si>
+  <si>
+    <t>FBA79379</t>
+  </si>
+  <si>
+    <t>AM-C45</t>
+  </si>
+  <si>
+    <t>FBA75676</t>
+  </si>
+  <si>
+    <t>AM-C4</t>
+  </si>
+  <si>
+    <t>FBA76414</t>
+  </si>
+  <si>
+    <t>AA-05</t>
+  </si>
+  <si>
+    <t>FBA79447</t>
+  </si>
+  <si>
+    <t>AM-W34</t>
+  </si>
+  <si>
+    <t>FBA78976</t>
+  </si>
+  <si>
+    <t>AA-22</t>
+  </si>
+  <si>
+    <t>FBA79446</t>
+  </si>
+  <si>
+    <t>AM-W33</t>
+  </si>
+  <si>
+    <t>FBA79103</t>
+  </si>
+  <si>
+    <t>AI-10</t>
+  </si>
+  <si>
+    <t>FBA79016</t>
+  </si>
+  <si>
+    <t>AM-C3a</t>
+  </si>
+  <si>
+    <t>FBA75683</t>
+  </si>
+  <si>
+    <t>AA-03</t>
+  </si>
+  <si>
+    <t>FBA79448</t>
+  </si>
+  <si>
+    <t>AM-W35</t>
+  </si>
+  <si>
+    <t>FBA75690</t>
+  </si>
+  <si>
+    <t>AM-C10</t>
+  </si>
+  <si>
+    <t>FBA76597</t>
+  </si>
+  <si>
+    <t>AA-06</t>
+  </si>
+  <si>
+    <t>FBA75675</t>
+  </si>
+  <si>
+    <t>AM-C3</t>
+  </si>
+  <si>
+    <t>FBA75678</t>
+  </si>
+  <si>
+    <t>AA-01</t>
+  </si>
+  <si>
+    <t>FBA78974</t>
+  </si>
+  <si>
+    <t>AA-20</t>
+  </si>
+  <si>
+    <t>FBA79105</t>
+  </si>
+  <si>
+    <t>AI-12</t>
+  </si>
+  <si>
+    <t>FBA78203</t>
+  </si>
+  <si>
+    <t>AM-C30</t>
+  </si>
+  <si>
+    <t>FBA76730</t>
+  </si>
+  <si>
+    <t>AM-C27</t>
+  </si>
+  <si>
+    <t>FBA75689</t>
+  </si>
+  <si>
+    <t>AM-W13</t>
+  </si>
+  <si>
+    <t>FBA79230</t>
+  </si>
+  <si>
+    <t>AM-W46</t>
+  </si>
+  <si>
+    <t>FBA78204</t>
+  </si>
+  <si>
+    <t>AM-C31</t>
+  </si>
+  <si>
+    <t>FBA78975</t>
+  </si>
+  <si>
+    <t>AA-21</t>
+  </si>
+  <si>
+    <t>FBA78424</t>
+  </si>
+  <si>
+    <t>AM-C37</t>
+  </si>
+  <si>
+    <t>FBA75681</t>
+  </si>
+  <si>
+    <t>AM-C7</t>
+  </si>
+  <si>
+    <t>FBA78961</t>
+  </si>
+  <si>
+    <t>AM-C40</t>
+  </si>
+  <si>
+    <t>FBA75692</t>
+  </si>
+  <si>
+    <t>AM-C11</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -310,6 +586,11 @@
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -343,7 +624,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -366,11 +647,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -420,6 +716,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2722,7 +3028,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E3AF619-DC76-4D87-9D69-4310FD74DCA6}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" customWidth="1"/>
@@ -2748,6 +3054,975 @@
         <v>5</v>
       </c>
     </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="20">
+        <v>9</v>
+      </c>
+      <c r="D2" s="21">
+        <v>20861.016949152545</v>
+      </c>
+      <c r="E2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="20">
+        <v>3</v>
+      </c>
+      <c r="D3" s="21">
+        <v>10546.610169491525</v>
+      </c>
+      <c r="E3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" s="20">
+        <v>3</v>
+      </c>
+      <c r="D4" s="21">
+        <v>8969.4915254237294</v>
+      </c>
+      <c r="E4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" s="20">
+        <v>2</v>
+      </c>
+      <c r="D5" s="21">
+        <v>8716.1016949152545</v>
+      </c>
+      <c r="E5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="20">
+        <v>2</v>
+      </c>
+      <c r="D6" s="21">
+        <v>5993.2203389830511</v>
+      </c>
+      <c r="E6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" s="20">
+        <v>2</v>
+      </c>
+      <c r="D7" s="21">
+        <v>4638.9830508474579</v>
+      </c>
+      <c r="E7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" s="20">
+        <v>3</v>
+      </c>
+      <c r="D8" s="21">
+        <v>3922.8813559322034</v>
+      </c>
+      <c r="E8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="20">
+        <v>1</v>
+      </c>
+      <c r="D9" s="21">
+        <v>2234.7457627118647</v>
+      </c>
+      <c r="E9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" s="20">
+        <v>1</v>
+      </c>
+      <c r="D10" s="21">
+        <v>1591.5254237288136</v>
+      </c>
+      <c r="E10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="20">
+        <v>1</v>
+      </c>
+      <c r="D11" s="21">
+        <v>1498.3050847457628</v>
+      </c>
+      <c r="E11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" s="20">
+        <v>1</v>
+      </c>
+      <c r="D12" s="21">
+        <v>769.49152542372883</v>
+      </c>
+      <c r="E12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="C13" s="20">
+        <v>1</v>
+      </c>
+      <c r="D13" s="21">
+        <v>472.88135593220341</v>
+      </c>
+      <c r="E13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="C14" s="20">
+        <v>0</v>
+      </c>
+      <c r="D14" s="21">
+        <v>0</v>
+      </c>
+      <c r="E14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="20">
+        <v>0</v>
+      </c>
+      <c r="D15" s="21">
+        <v>0</v>
+      </c>
+      <c r="E15" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" s="20">
+        <v>0</v>
+      </c>
+      <c r="D16" s="21">
+        <v>0</v>
+      </c>
+      <c r="E16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="C17" s="20">
+        <v>0</v>
+      </c>
+      <c r="D17" s="21">
+        <v>0</v>
+      </c>
+      <c r="E17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" s="20">
+        <v>0</v>
+      </c>
+      <c r="D18" s="21">
+        <v>0</v>
+      </c>
+      <c r="E18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="C19" s="20">
+        <v>0</v>
+      </c>
+      <c r="D19" s="21">
+        <v>0</v>
+      </c>
+      <c r="E19" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="C20" s="20">
+        <v>0</v>
+      </c>
+      <c r="D20" s="21">
+        <v>0</v>
+      </c>
+      <c r="E20" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="C21" s="20">
+        <v>0</v>
+      </c>
+      <c r="D21" s="21">
+        <v>0</v>
+      </c>
+      <c r="E21" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="C22" s="20">
+        <v>0</v>
+      </c>
+      <c r="D22" s="21">
+        <v>0</v>
+      </c>
+      <c r="E22" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" s="20">
+        <v>0</v>
+      </c>
+      <c r="D23" s="21">
+        <v>0</v>
+      </c>
+      <c r="E23" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C24" s="20">
+        <v>0</v>
+      </c>
+      <c r="D24" s="21">
+        <v>0</v>
+      </c>
+      <c r="E24" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="C25" s="20">
+        <v>0</v>
+      </c>
+      <c r="D25" s="21">
+        <v>0</v>
+      </c>
+      <c r="E25" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="C26" s="20">
+        <v>0</v>
+      </c>
+      <c r="D26" s="21">
+        <v>0</v>
+      </c>
+      <c r="E26" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="C27" s="20">
+        <v>0</v>
+      </c>
+      <c r="D27" s="21">
+        <v>0</v>
+      </c>
+      <c r="E27" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="C28" s="20">
+        <v>0</v>
+      </c>
+      <c r="D28" s="21">
+        <v>0</v>
+      </c>
+      <c r="E28" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="C29" s="20">
+        <v>0</v>
+      </c>
+      <c r="D29" s="21">
+        <v>0</v>
+      </c>
+      <c r="E29" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="C30" s="20">
+        <v>0</v>
+      </c>
+      <c r="D30" s="21">
+        <v>0</v>
+      </c>
+      <c r="E30" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="B31" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="C31" s="20">
+        <v>0</v>
+      </c>
+      <c r="D31" s="21">
+        <v>0</v>
+      </c>
+      <c r="E31" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="C32" s="20">
+        <v>0</v>
+      </c>
+      <c r="D32" s="21">
+        <v>0</v>
+      </c>
+      <c r="E32" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="20">
+        <v>0</v>
+      </c>
+      <c r="D33" s="21">
+        <v>0</v>
+      </c>
+      <c r="E33" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="C34" s="20">
+        <v>0</v>
+      </c>
+      <c r="D34" s="21">
+        <v>0</v>
+      </c>
+      <c r="E34" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="B35" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="C35" s="20">
+        <v>0</v>
+      </c>
+      <c r="D35" s="21">
+        <v>0</v>
+      </c>
+      <c r="E35" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="B36" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="C36" s="20">
+        <v>0</v>
+      </c>
+      <c r="D36" s="21">
+        <v>0</v>
+      </c>
+      <c r="E36" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="B37" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="C37" s="20">
+        <v>0</v>
+      </c>
+      <c r="D37" s="21">
+        <v>0</v>
+      </c>
+      <c r="E37" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="B38" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="C38" s="20">
+        <v>0</v>
+      </c>
+      <c r="D38" s="21">
+        <v>0</v>
+      </c>
+      <c r="E38" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B39" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="C39" s="20">
+        <v>0</v>
+      </c>
+      <c r="D39" s="21">
+        <v>0</v>
+      </c>
+      <c r="E39" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B40" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="C40" s="20">
+        <v>0</v>
+      </c>
+      <c r="D40" s="21">
+        <v>0</v>
+      </c>
+      <c r="E40" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B41" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="C41" s="20">
+        <v>0</v>
+      </c>
+      <c r="D41" s="21">
+        <v>0</v>
+      </c>
+      <c r="E41" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="B42" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="C42" s="20">
+        <v>0</v>
+      </c>
+      <c r="D42" s="21">
+        <v>0</v>
+      </c>
+      <c r="E42" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="C43" s="20">
+        <v>0</v>
+      </c>
+      <c r="D43" s="21">
+        <v>0</v>
+      </c>
+      <c r="E43" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="B44" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="C44" s="20">
+        <v>0</v>
+      </c>
+      <c r="D44" s="21">
+        <v>0</v>
+      </c>
+      <c r="E44" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="B45" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="C45" s="20">
+        <v>0</v>
+      </c>
+      <c r="D45" s="21">
+        <v>0</v>
+      </c>
+      <c r="E45" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="B46" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="C46" s="20">
+        <v>0</v>
+      </c>
+      <c r="D46" s="21">
+        <v>0</v>
+      </c>
+      <c r="E46" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="B47" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="C47" s="20">
+        <v>0</v>
+      </c>
+      <c r="D47" s="21">
+        <v>0</v>
+      </c>
+      <c r="E47" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B48" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C48" s="20">
+        <v>0</v>
+      </c>
+      <c r="D48" s="21">
+        <v>0</v>
+      </c>
+      <c r="E48" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="B49" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="C49" s="20">
+        <v>0</v>
+      </c>
+      <c r="D49" s="21">
+        <v>0</v>
+      </c>
+      <c r="E49" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="B50" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C50" s="20">
+        <v>0</v>
+      </c>
+      <c r="D50" s="21">
+        <v>0</v>
+      </c>
+      <c r="E50" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B51" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C51" s="20">
+        <v>0</v>
+      </c>
+      <c r="D51" s="21">
+        <v>0</v>
+      </c>
+      <c r="E51" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="B52" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="C52" s="20">
+        <v>0</v>
+      </c>
+      <c r="D52" s="21">
+        <v>0</v>
+      </c>
+      <c r="E52" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="B53" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="C53" s="20">
+        <v>0</v>
+      </c>
+      <c r="D53" s="21">
+        <v>0</v>
+      </c>
+      <c r="E53" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="B54" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="C54" s="20">
+        <v>0</v>
+      </c>
+      <c r="D54" s="21">
+        <v>0</v>
+      </c>
+      <c r="E54" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="B55" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="C55" s="20">
+        <v>0</v>
+      </c>
+      <c r="D55" s="21">
+        <v>0</v>
+      </c>
+      <c r="E55" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="B56" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="C56" s="20">
+        <v>0</v>
+      </c>
+      <c r="D56" s="21">
+        <v>0</v>
+      </c>
+      <c r="E56" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="B57" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="C57" s="20">
+        <v>0</v>
+      </c>
+      <c r="D57" s="21">
+        <v>0</v>
+      </c>
+      <c r="E57" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="B58" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="C58" s="20">
+        <v>0</v>
+      </c>
+      <c r="D58" s="21">
+        <v>0</v>
+      </c>
+      <c r="E58" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
